--- a/Data/EXCEL/Transfer/salemon/202206/6706-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/6706-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23564B7A-70BD-4C42-A613-598A88E15573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{26C627B7-9041-4E65-BF1E-B58AC15BBDA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="6706-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -261,7 +261,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF008000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -277,7 +277,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
+      <color rgb="FFFF0000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -1218,18 +1218,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q50"/>
+  <dimension ref="A1:Q51"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="12.5" customWidth="1"/>
-    <col min="8" max="8" width="10.5" customWidth="1"/>
-    <col min="9" max="11" width="11" customWidth="1"/>
-    <col min="12" max="13" width="10.5" customWidth="1"/>
-    <col min="14" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="11.125" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="5" width="12.5" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="14.375" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="11" width="12.5" customWidth="1"/>
+    <col min="12" max="13" width="12" customWidth="1"/>
+    <col min="14" max="16" width="12.5" customWidth="1"/>
+    <col min="17" max="17" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1382,1650 +1382,1650 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>161</v>
+        <v>161.5</v>
       </c>
       <c r="C5" s="7">
-        <v>161.5</v>
+        <v>125.5</v>
       </c>
       <c r="D5" s="7">
-        <v>169</v>
+        <v>167.5</v>
       </c>
       <c r="E5" s="7">
-        <v>146.5</v>
+        <v>125</v>
       </c>
       <c r="F5" s="8">
-        <v>1</v>
+        <v>-36</v>
       </c>
       <c r="G5" s="8">
-        <v>0.62</v>
+        <v>-22.29</v>
       </c>
       <c r="H5" s="9">
-        <v>4.51</v>
+        <v>4.75</v>
       </c>
       <c r="I5" s="10">
-        <v>-17.5</v>
-      </c>
-      <c r="J5" s="10">
-        <v>-4.57</v>
+        <v>5.38</v>
+      </c>
+      <c r="J5" s="8">
+        <v>-0.75</v>
       </c>
       <c r="K5" s="9">
-        <v>28.14</v>
-      </c>
-      <c r="L5" s="8">
-        <v>34.9</v>
+        <v>32.89</v>
+      </c>
+      <c r="L5" s="10">
+        <v>28.2</v>
       </c>
       <c r="M5" s="9">
-        <v>4.51</v>
+        <v>4.75</v>
       </c>
       <c r="N5" s="10">
-        <v>-17.5</v>
-      </c>
-      <c r="O5" s="10">
-        <v>-4.57</v>
+        <v>5.38</v>
+      </c>
+      <c r="O5" s="8">
+        <v>-0.75</v>
       </c>
       <c r="P5" s="9">
-        <v>28.14</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>34.9</v>
+        <v>32.89</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>28.2</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="C6" s="7">
-        <v>160.5</v>
+        <v>161.5</v>
       </c>
       <c r="D6" s="7">
-        <v>193.5</v>
+        <v>169</v>
       </c>
       <c r="E6" s="7">
-        <v>151</v>
+        <v>146.5</v>
       </c>
       <c r="F6" s="10">
-        <v>-34</v>
+        <v>1</v>
       </c>
       <c r="G6" s="10">
-        <v>-17.48</v>
+        <v>0.62</v>
       </c>
       <c r="H6" s="9">
-        <v>5.47</v>
-      </c>
-      <c r="I6" s="10">
-        <v>-9.81</v>
+        <v>4.51</v>
+      </c>
+      <c r="I6" s="8">
+        <v>-17.5</v>
       </c>
       <c r="J6" s="8">
-        <v>27.2</v>
+        <v>-4.57</v>
       </c>
       <c r="K6" s="9">
-        <v>23.63</v>
-      </c>
-      <c r="L6" s="8">
-        <v>46.4</v>
+        <v>28.14</v>
+      </c>
+      <c r="L6" s="10">
+        <v>34.9</v>
       </c>
       <c r="M6" s="9">
-        <v>5.47</v>
-      </c>
-      <c r="N6" s="10">
-        <v>-9.81</v>
+        <v>4.51</v>
+      </c>
+      <c r="N6" s="8">
+        <v>-17.5</v>
       </c>
       <c r="O6" s="8">
-        <v>27.2</v>
+        <v>-4.57</v>
       </c>
       <c r="P6" s="9">
-        <v>23.63</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>46.4</v>
+        <v>28.14</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>34.9</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B7" s="7">
-        <v>202.5</v>
+        <v>193</v>
       </c>
       <c r="C7" s="7">
-        <v>194.5</v>
+        <v>160.5</v>
       </c>
       <c r="D7" s="7">
-        <v>213.5</v>
+        <v>193.5</v>
       </c>
       <c r="E7" s="7">
-        <v>175</v>
-      </c>
-      <c r="F7" s="10">
-        <v>-4.5</v>
-      </c>
-      <c r="G7" s="10">
-        <v>-2.2599999999999998</v>
+        <v>151</v>
+      </c>
+      <c r="F7" s="8">
+        <v>-34</v>
+      </c>
+      <c r="G7" s="8">
+        <v>-17.48</v>
       </c>
       <c r="H7" s="9">
-        <v>6.06</v>
+        <v>5.47</v>
       </c>
       <c r="I7" s="8">
-        <v>0.12</v>
-      </c>
-      <c r="J7" s="8">
-        <v>49.1</v>
+        <v>-9.81</v>
+      </c>
+      <c r="J7" s="10">
+        <v>27.2</v>
       </c>
       <c r="K7" s="9">
-        <v>18.170000000000002</v>
-      </c>
-      <c r="L7" s="8">
-        <v>53.4</v>
+        <v>23.63</v>
+      </c>
+      <c r="L7" s="10">
+        <v>46.4</v>
       </c>
       <c r="M7" s="9">
-        <v>6.06</v>
+        <v>5.47</v>
       </c>
       <c r="N7" s="8">
-        <v>0.12</v>
-      </c>
-      <c r="O7" s="8">
-        <v>49.1</v>
+        <v>-9.81</v>
+      </c>
+      <c r="O7" s="10">
+        <v>27.2</v>
       </c>
       <c r="P7" s="9">
-        <v>18.170000000000002</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>53.4</v>
+        <v>23.63</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>46.4</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" s="7">
-        <v>225</v>
+        <v>202.5</v>
       </c>
       <c r="C8" s="7">
-        <v>199</v>
+        <v>194.5</v>
       </c>
       <c r="D8" s="7">
-        <v>256</v>
+        <v>213.5</v>
       </c>
       <c r="E8" s="7">
-        <v>198</v>
-      </c>
-      <c r="F8" s="10">
-        <v>-22.5</v>
-      </c>
-      <c r="G8" s="10">
-        <v>-10.16</v>
+        <v>175</v>
+      </c>
+      <c r="F8" s="8">
+        <v>-4.5</v>
+      </c>
+      <c r="G8" s="8">
+        <v>-2.2599999999999998</v>
       </c>
       <c r="H8" s="9">
-        <v>6.05</v>
-      </c>
-      <c r="I8" s="9">
-        <v>0</v>
-      </c>
-      <c r="J8" s="8">
-        <v>51.6</v>
+        <v>6.06</v>
+      </c>
+      <c r="I8" s="10">
+        <v>0.12</v>
+      </c>
+      <c r="J8" s="10">
+        <v>49.1</v>
       </c>
       <c r="K8" s="9">
-        <v>12.11</v>
-      </c>
-      <c r="L8" s="8">
-        <v>55.6</v>
+        <v>18.170000000000002</v>
+      </c>
+      <c r="L8" s="10">
+        <v>53.4</v>
       </c>
       <c r="M8" s="9">
-        <v>6.05</v>
-      </c>
-      <c r="N8" s="9">
-        <v>0</v>
-      </c>
-      <c r="O8" s="8">
-        <v>51.6</v>
+        <v>6.06</v>
+      </c>
+      <c r="N8" s="10">
+        <v>0.12</v>
+      </c>
+      <c r="O8" s="10">
+        <v>49.1</v>
       </c>
       <c r="P8" s="9">
-        <v>12.11</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>55.6</v>
+        <v>18.170000000000002</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>53.4</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B9" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C9" s="7">
-        <v>221.5</v>
+        <v>199</v>
       </c>
       <c r="D9" s="7">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E9" s="7">
-        <v>213.5</v>
+        <v>198</v>
       </c>
       <c r="F9" s="8">
-        <v>2.5</v>
+        <v>-22.5</v>
       </c>
       <c r="G9" s="8">
-        <v>1.1399999999999999</v>
+        <v>-10.16</v>
       </c>
       <c r="H9" s="9">
         <v>6.05</v>
       </c>
-      <c r="I9" s="8">
-        <v>5.08</v>
-      </c>
-      <c r="J9" s="8">
-        <v>59.9</v>
+      <c r="I9" s="9">
+        <v>0</v>
+      </c>
+      <c r="J9" s="10">
+        <v>51.6</v>
       </c>
       <c r="K9" s="9">
-        <v>6.05</v>
-      </c>
-      <c r="L9" s="8">
-        <v>59.9</v>
+        <v>12.11</v>
+      </c>
+      <c r="L9" s="10">
+        <v>55.6</v>
       </c>
       <c r="M9" s="9">
         <v>6.05</v>
       </c>
-      <c r="N9" s="8">
-        <v>5.08</v>
-      </c>
-      <c r="O9" s="8">
-        <v>59.9</v>
+      <c r="N9" s="9">
+        <v>0</v>
+      </c>
+      <c r="O9" s="10">
+        <v>51.6</v>
       </c>
       <c r="P9" s="9">
-        <v>6.05</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>59.9</v>
+        <v>12.11</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>55.6</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B10" s="7">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="C10" s="7">
-        <v>219</v>
+        <v>221.5</v>
       </c>
       <c r="D10" s="7">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="E10" s="7">
-        <v>205.5</v>
-      </c>
-      <c r="F10" s="8">
-        <v>9.5</v>
-      </c>
-      <c r="G10" s="8">
-        <v>4.53</v>
+        <v>213.5</v>
+      </c>
+      <c r="F10" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="G10" s="10">
+        <v>1.1399999999999999</v>
       </c>
       <c r="H10" s="9">
-        <v>5.76</v>
-      </c>
-      <c r="I10" s="8">
-        <v>4.78</v>
-      </c>
-      <c r="J10" s="8">
-        <v>69.599999999999994</v>
+        <v>6.05</v>
+      </c>
+      <c r="I10" s="10">
+        <v>5.08</v>
+      </c>
+      <c r="J10" s="10">
+        <v>59.9</v>
       </c>
       <c r="K10" s="9">
-        <v>57.15</v>
-      </c>
-      <c r="L10" s="8">
-        <v>81.099999999999994</v>
+        <v>6.05</v>
+      </c>
+      <c r="L10" s="10">
+        <v>59.9</v>
       </c>
       <c r="M10" s="9">
-        <v>5.76</v>
-      </c>
-      <c r="N10" s="8">
-        <v>4.78</v>
-      </c>
-      <c r="O10" s="8">
-        <v>69.599999999999994</v>
+        <v>6.05</v>
+      </c>
+      <c r="N10" s="10">
+        <v>5.08</v>
+      </c>
+      <c r="O10" s="10">
+        <v>59.9</v>
       </c>
       <c r="P10" s="9">
-        <v>57.15</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>81.099999999999994</v>
+        <v>6.05</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>59.9</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B11" s="7">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C11" s="7">
-        <v>209.5</v>
+        <v>219</v>
       </c>
       <c r="D11" s="7">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="E11" s="7">
-        <v>200</v>
+        <v>205.5</v>
       </c>
       <c r="F11" s="10">
-        <v>-0.5</v>
+        <v>9.5</v>
       </c>
       <c r="G11" s="10">
-        <v>-0.24</v>
+        <v>4.53</v>
       </c>
       <c r="H11" s="9">
-        <v>5.5</v>
-      </c>
-      <c r="I11" s="8">
-        <v>7.38</v>
-      </c>
-      <c r="J11" s="8">
-        <v>98.2</v>
+        <v>5.76</v>
+      </c>
+      <c r="I11" s="10">
+        <v>4.78</v>
+      </c>
+      <c r="J11" s="10">
+        <v>69.599999999999994</v>
       </c>
       <c r="K11" s="9">
-        <v>51.39</v>
-      </c>
-      <c r="L11" s="8">
-        <v>82.4</v>
+        <v>57.15</v>
+      </c>
+      <c r="L11" s="10">
+        <v>81.099999999999994</v>
       </c>
       <c r="M11" s="9">
-        <v>5.5</v>
-      </c>
-      <c r="N11" s="8">
-        <v>7.38</v>
-      </c>
-      <c r="O11" s="8">
-        <v>98.2</v>
+        <v>5.76</v>
+      </c>
+      <c r="N11" s="10">
+        <v>4.78</v>
+      </c>
+      <c r="O11" s="10">
+        <v>69.599999999999994</v>
       </c>
       <c r="P11" s="9">
-        <v>51.39</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>82.4</v>
+        <v>57.15</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>81.099999999999994</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B12" s="7">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="C12" s="7">
-        <v>210</v>
+        <v>209.5</v>
       </c>
       <c r="D12" s="7">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="E12" s="7">
-        <v>157</v>
+        <v>200</v>
       </c>
       <c r="F12" s="8">
-        <v>36.5</v>
+        <v>-0.5</v>
       </c>
       <c r="G12" s="8">
-        <v>21.04</v>
+        <v>-0.24</v>
       </c>
       <c r="H12" s="9">
-        <v>5.12</v>
-      </c>
-      <c r="I12" s="8">
-        <v>0.96</v>
-      </c>
-      <c r="J12" s="8">
-        <v>96</v>
+        <v>5.5</v>
+      </c>
+      <c r="I12" s="10">
+        <v>7.38</v>
+      </c>
+      <c r="J12" s="10">
+        <v>98.2</v>
       </c>
       <c r="K12" s="9">
-        <v>45.89</v>
-      </c>
-      <c r="L12" s="8">
-        <v>80.7</v>
+        <v>51.39</v>
+      </c>
+      <c r="L12" s="10">
+        <v>82.4</v>
       </c>
       <c r="M12" s="9">
-        <v>5.12</v>
-      </c>
-      <c r="N12" s="8">
-        <v>0.96</v>
-      </c>
-      <c r="O12" s="8">
-        <v>96</v>
+        <v>5.5</v>
+      </c>
+      <c r="N12" s="10">
+        <v>7.38</v>
+      </c>
+      <c r="O12" s="10">
+        <v>98.2</v>
       </c>
       <c r="P12" s="9">
-        <v>45.89</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>80.7</v>
+        <v>51.39</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>82.4</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B13" s="7">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="C13" s="7">
-        <v>173.5</v>
+        <v>210</v>
       </c>
       <c r="D13" s="7">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="E13" s="7">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="F13" s="10">
-        <v>-16.5</v>
+        <v>36.5</v>
       </c>
       <c r="G13" s="10">
-        <v>-8.68</v>
+        <v>21.04</v>
       </c>
       <c r="H13" s="9">
-        <v>5.07</v>
-      </c>
-      <c r="I13" s="8">
-        <v>0.74</v>
-      </c>
-      <c r="J13" s="8">
-        <v>126.7</v>
+        <v>5.12</v>
+      </c>
+      <c r="I13" s="10">
+        <v>0.96</v>
+      </c>
+      <c r="J13" s="10">
+        <v>96</v>
       </c>
       <c r="K13" s="9">
-        <v>40.770000000000003</v>
-      </c>
-      <c r="L13" s="8">
-        <v>79</v>
+        <v>45.89</v>
+      </c>
+      <c r="L13" s="10">
+        <v>80.7</v>
       </c>
       <c r="M13" s="9">
-        <v>5.07</v>
-      </c>
-      <c r="N13" s="8">
-        <v>0.74</v>
-      </c>
-      <c r="O13" s="8">
-        <v>126.7</v>
+        <v>5.12</v>
+      </c>
+      <c r="N13" s="10">
+        <v>0.96</v>
+      </c>
+      <c r="O13" s="10">
+        <v>96</v>
       </c>
       <c r="P13" s="9">
-        <v>40.770000000000003</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>79</v>
+        <v>45.89</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>80.7</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B14" s="7">
-        <v>211.5</v>
+        <v>191</v>
       </c>
       <c r="C14" s="7">
-        <v>190</v>
+        <v>173.5</v>
       </c>
       <c r="D14" s="7">
-        <v>213.5</v>
+        <v>201</v>
       </c>
       <c r="E14" s="7">
-        <v>158</v>
-      </c>
-      <c r="F14" s="10">
-        <v>-18</v>
-      </c>
-      <c r="G14" s="10">
-        <v>-8.65</v>
+        <v>167</v>
+      </c>
+      <c r="F14" s="8">
+        <v>-16.5</v>
+      </c>
+      <c r="G14" s="8">
+        <v>-8.68</v>
       </c>
       <c r="H14" s="9">
-        <v>5.03</v>
-      </c>
-      <c r="I14" s="8">
-        <v>0.17</v>
-      </c>
-      <c r="J14" s="8">
-        <v>144.19999999999999</v>
+        <v>5.07</v>
+      </c>
+      <c r="I14" s="10">
+        <v>0.74</v>
+      </c>
+      <c r="J14" s="10">
+        <v>126.7</v>
       </c>
       <c r="K14" s="9">
-        <v>35.700000000000003</v>
-      </c>
-      <c r="L14" s="8">
-        <v>73.8</v>
+        <v>40.770000000000003</v>
+      </c>
+      <c r="L14" s="10">
+        <v>79</v>
       </c>
       <c r="M14" s="9">
-        <v>5.03</v>
-      </c>
-      <c r="N14" s="8">
-        <v>0.17</v>
-      </c>
-      <c r="O14" s="8">
-        <v>144.19999999999999</v>
+        <v>5.07</v>
+      </c>
+      <c r="N14" s="10">
+        <v>0.74</v>
+      </c>
+      <c r="O14" s="10">
+        <v>126.7</v>
       </c>
       <c r="P14" s="9">
-        <v>35.700000000000003</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>73.8</v>
+        <v>40.770000000000003</v>
+      </c>
+      <c r="Q14" s="10">
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B15" s="7">
-        <v>173.5</v>
+        <v>211.5</v>
       </c>
       <c r="C15" s="7">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="D15" s="7">
-        <v>225</v>
+        <v>213.5</v>
       </c>
       <c r="E15" s="7">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="F15" s="8">
-        <v>35</v>
+        <v>-18</v>
       </c>
       <c r="G15" s="8">
-        <v>20.23</v>
+        <v>-8.65</v>
       </c>
       <c r="H15" s="9">
-        <v>5.0199999999999996</v>
-      </c>
-      <c r="I15" s="8">
-        <v>4.9400000000000004</v>
-      </c>
-      <c r="J15" s="8">
-        <v>146.6</v>
+        <v>5.03</v>
+      </c>
+      <c r="I15" s="10">
+        <v>0.17</v>
+      </c>
+      <c r="J15" s="10">
+        <v>144.19999999999999</v>
       </c>
       <c r="K15" s="9">
-        <v>30.67</v>
-      </c>
-      <c r="L15" s="8">
-        <v>65.900000000000006</v>
+        <v>35.700000000000003</v>
+      </c>
+      <c r="L15" s="10">
+        <v>73.8</v>
       </c>
       <c r="M15" s="9">
-        <v>5.0199999999999996</v>
-      </c>
-      <c r="N15" s="8">
-        <v>4.9400000000000004</v>
-      </c>
-      <c r="O15" s="8">
-        <v>146.6</v>
+        <v>5.03</v>
+      </c>
+      <c r="N15" s="10">
+        <v>0.17</v>
+      </c>
+      <c r="O15" s="10">
+        <v>144.19999999999999</v>
       </c>
       <c r="P15" s="9">
-        <v>30.67</v>
-      </c>
-      <c r="Q15" s="8">
-        <v>65.900000000000006</v>
+        <v>35.700000000000003</v>
+      </c>
+      <c r="Q15" s="10">
+        <v>73.8</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B16" s="7">
-        <v>165</v>
+        <v>173.5</v>
       </c>
       <c r="C16" s="7">
-        <v>173</v>
+        <v>208</v>
       </c>
       <c r="D16" s="7">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="E16" s="7">
-        <v>164.5</v>
-      </c>
-      <c r="F16" s="8">
-        <v>10</v>
-      </c>
-      <c r="G16" s="8">
-        <v>6.13</v>
+        <v>167</v>
+      </c>
+      <c r="F16" s="10">
+        <v>35</v>
+      </c>
+      <c r="G16" s="10">
+        <v>20.23</v>
       </c>
       <c r="H16" s="9">
-        <v>4.79</v>
-      </c>
-      <c r="I16" s="8">
-        <v>1.32</v>
-      </c>
-      <c r="J16" s="8">
-        <v>83.8</v>
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="I16" s="10">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="J16" s="10">
+        <v>146.6</v>
       </c>
       <c r="K16" s="9">
-        <v>25.65</v>
-      </c>
-      <c r="L16" s="8">
-        <v>56</v>
+        <v>30.67</v>
+      </c>
+      <c r="L16" s="10">
+        <v>65.900000000000006</v>
       </c>
       <c r="M16" s="9">
-        <v>4.79</v>
-      </c>
-      <c r="N16" s="8">
-        <v>1.32</v>
-      </c>
-      <c r="O16" s="8">
-        <v>83.8</v>
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="N16" s="10">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="O16" s="10">
+        <v>146.6</v>
       </c>
       <c r="P16" s="9">
-        <v>25.65</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>56</v>
+        <v>30.67</v>
+      </c>
+      <c r="Q16" s="10">
+        <v>65.900000000000006</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B17" s="7">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="C17" s="7">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D17" s="7">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E17" s="7">
-        <v>129.5</v>
+        <v>164.5</v>
       </c>
       <c r="F17" s="10">
-        <v>-21</v>
+        <v>10</v>
       </c>
       <c r="G17" s="10">
-        <v>-11.41</v>
+        <v>6.13</v>
       </c>
       <c r="H17" s="9">
-        <v>4.72</v>
-      </c>
-      <c r="I17" s="8">
-        <v>9.93</v>
-      </c>
-      <c r="J17" s="8">
-        <v>86.6</v>
+        <v>4.79</v>
+      </c>
+      <c r="I17" s="10">
+        <v>1.32</v>
+      </c>
+      <c r="J17" s="10">
+        <v>83.8</v>
       </c>
       <c r="K17" s="9">
-        <v>20.86</v>
-      </c>
-      <c r="L17" s="8">
-        <v>50.7</v>
+        <v>25.65</v>
+      </c>
+      <c r="L17" s="10">
+        <v>56</v>
       </c>
       <c r="M17" s="9">
-        <v>4.72</v>
-      </c>
-      <c r="N17" s="8">
-        <v>9.93</v>
-      </c>
-      <c r="O17" s="8">
-        <v>86.6</v>
+        <v>4.79</v>
+      </c>
+      <c r="N17" s="10">
+        <v>1.32</v>
+      </c>
+      <c r="O17" s="10">
+        <v>83.8</v>
       </c>
       <c r="P17" s="9">
-        <v>20.86</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>50.7</v>
+        <v>25.65</v>
+      </c>
+      <c r="Q17" s="10">
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B18" s="7">
         <v>184</v>
       </c>
       <c r="C18" s="7">
+        <v>163</v>
+      </c>
+      <c r="D18" s="7">
         <v>184</v>
       </c>
-      <c r="D18" s="7">
-        <v>233</v>
-      </c>
       <c r="E18" s="7">
-        <v>177</v>
+        <v>129.5</v>
       </c>
       <c r="F18" s="8">
-        <v>3</v>
+        <v>-21</v>
       </c>
       <c r="G18" s="8">
-        <v>1.66</v>
+        <v>-11.41</v>
       </c>
       <c r="H18" s="9">
-        <v>4.3</v>
-      </c>
-      <c r="I18" s="8">
-        <v>5.73</v>
-      </c>
-      <c r="J18" s="8">
-        <v>79.099999999999994</v>
+        <v>4.72</v>
+      </c>
+      <c r="I18" s="10">
+        <v>9.93</v>
+      </c>
+      <c r="J18" s="10">
+        <v>86.6</v>
       </c>
       <c r="K18" s="9">
-        <v>16.14</v>
-      </c>
-      <c r="L18" s="8">
-        <v>42.7</v>
+        <v>20.86</v>
+      </c>
+      <c r="L18" s="10">
+        <v>50.7</v>
       </c>
       <c r="M18" s="9">
-        <v>4.3</v>
-      </c>
-      <c r="N18" s="8">
-        <v>5.73</v>
-      </c>
-      <c r="O18" s="8">
-        <v>79.099999999999994</v>
+        <v>4.72</v>
+      </c>
+      <c r="N18" s="10">
+        <v>9.93</v>
+      </c>
+      <c r="O18" s="10">
+        <v>86.6</v>
       </c>
       <c r="P18" s="9">
-        <v>16.14</v>
-      </c>
-      <c r="Q18" s="8">
-        <v>42.7</v>
+        <v>20.86</v>
+      </c>
+      <c r="Q18" s="10">
+        <v>50.7</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B19" s="7">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="C19" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D19" s="7">
-        <v>181</v>
+        <v>233</v>
       </c>
       <c r="E19" s="7">
-        <v>152.5</v>
-      </c>
-      <c r="F19" s="8">
-        <v>22</v>
-      </c>
-      <c r="G19" s="8">
-        <v>13.84</v>
+        <v>177</v>
+      </c>
+      <c r="F19" s="10">
+        <v>3</v>
+      </c>
+      <c r="G19" s="10">
+        <v>1.66</v>
       </c>
       <c r="H19" s="9">
-        <v>4.0599999999999996</v>
-      </c>
-      <c r="I19" s="8">
-        <v>1.8</v>
-      </c>
-      <c r="J19" s="8">
-        <v>40.200000000000003</v>
+        <v>4.3</v>
+      </c>
+      <c r="I19" s="10">
+        <v>5.73</v>
+      </c>
+      <c r="J19" s="10">
+        <v>79.099999999999994</v>
       </c>
       <c r="K19" s="9">
-        <v>11.84</v>
-      </c>
-      <c r="L19" s="8">
-        <v>32.799999999999997</v>
+        <v>16.14</v>
+      </c>
+      <c r="L19" s="10">
+        <v>42.7</v>
       </c>
       <c r="M19" s="9">
-        <v>4.0599999999999996</v>
-      </c>
-      <c r="N19" s="8">
-        <v>1.8</v>
-      </c>
-      <c r="O19" s="8">
-        <v>40.200000000000003</v>
+        <v>4.3</v>
+      </c>
+      <c r="N19" s="10">
+        <v>5.73</v>
+      </c>
+      <c r="O19" s="10">
+        <v>79.099999999999994</v>
       </c>
       <c r="P19" s="9">
-        <v>11.84</v>
-      </c>
-      <c r="Q19" s="8">
-        <v>32.799999999999997</v>
+        <v>16.14</v>
+      </c>
+      <c r="Q19" s="10">
+        <v>42.7</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B20" s="7">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C20" s="7">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="D20" s="7">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="E20" s="7">
-        <v>151</v>
-      </c>
-      <c r="F20" s="8">
-        <v>3</v>
-      </c>
-      <c r="G20" s="8">
-        <v>1.92</v>
+        <v>152.5</v>
+      </c>
+      <c r="F20" s="10">
+        <v>22</v>
+      </c>
+      <c r="G20" s="10">
+        <v>13.84</v>
       </c>
       <c r="H20" s="9">
-        <v>3.99</v>
-      </c>
-      <c r="I20" s="8">
-        <v>5.44</v>
-      </c>
-      <c r="J20" s="8">
-        <v>29.7</v>
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="I20" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="J20" s="10">
+        <v>40.200000000000003</v>
       </c>
       <c r="K20" s="9">
-        <v>7.78</v>
-      </c>
-      <c r="L20" s="8">
-        <v>29.3</v>
+        <v>11.84</v>
+      </c>
+      <c r="L20" s="10">
+        <v>32.799999999999997</v>
       </c>
       <c r="M20" s="9">
-        <v>3.99</v>
-      </c>
-      <c r="N20" s="8">
-        <v>5.44</v>
-      </c>
-      <c r="O20" s="8">
-        <v>29.7</v>
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="N20" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="O20" s="10">
+        <v>40.200000000000003</v>
       </c>
       <c r="P20" s="9">
-        <v>7.78</v>
-      </c>
-      <c r="Q20" s="8">
-        <v>29.3</v>
+        <v>11.84</v>
+      </c>
+      <c r="Q20" s="10">
+        <v>32.799999999999997</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B21" s="7">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C21" s="7">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D21" s="7">
-        <v>172.5</v>
+        <v>167</v>
       </c>
       <c r="E21" s="7">
-        <v>149.5</v>
+        <v>151</v>
       </c>
       <c r="F21" s="10">
-        <v>-11</v>
+        <v>3</v>
       </c>
       <c r="G21" s="10">
-        <v>-6.59</v>
+        <v>1.92</v>
       </c>
       <c r="H21" s="9">
-        <v>3.79</v>
-      </c>
-      <c r="I21" s="8">
-        <v>11.4</v>
-      </c>
-      <c r="J21" s="8">
-        <v>28.8</v>
+        <v>3.99</v>
+      </c>
+      <c r="I21" s="10">
+        <v>5.44</v>
+      </c>
+      <c r="J21" s="10">
+        <v>29.7</v>
       </c>
       <c r="K21" s="9">
-        <v>3.79</v>
-      </c>
-      <c r="L21" s="8">
-        <v>28.8</v>
+        <v>7.78</v>
+      </c>
+      <c r="L21" s="10">
+        <v>29.3</v>
       </c>
       <c r="M21" s="9">
-        <v>3.79</v>
-      </c>
-      <c r="N21" s="8">
-        <v>11.4</v>
-      </c>
-      <c r="O21" s="8">
-        <v>28.8</v>
+        <v>3.99</v>
+      </c>
+      <c r="N21" s="10">
+        <v>5.44</v>
+      </c>
+      <c r="O21" s="10">
+        <v>29.7</v>
       </c>
       <c r="P21" s="9">
-        <v>3.79</v>
-      </c>
-      <c r="Q21" s="8">
-        <v>28.8</v>
+        <v>7.78</v>
+      </c>
+      <c r="Q21" s="10">
+        <v>29.3</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B22" s="7">
-        <v>167.5</v>
+        <v>166</v>
       </c>
       <c r="C22" s="7">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="D22" s="7">
-        <v>182.5</v>
+        <v>172.5</v>
       </c>
       <c r="E22" s="7">
-        <v>152</v>
+        <v>149.5</v>
       </c>
       <c r="F22" s="8">
-        <v>0.5</v>
+        <v>-11</v>
       </c>
       <c r="G22" s="8">
-        <v>0.3</v>
+        <v>-6.59</v>
       </c>
       <c r="H22" s="9">
-        <v>3.4</v>
-      </c>
-      <c r="I22" s="8">
-        <v>22.5</v>
-      </c>
-      <c r="J22" s="8">
-        <v>17.399999999999999</v>
+        <v>3.79</v>
+      </c>
+      <c r="I22" s="10">
+        <v>11.4</v>
+      </c>
+      <c r="J22" s="10">
+        <v>28.8</v>
       </c>
       <c r="K22" s="9">
-        <v>31.56</v>
+        <v>3.79</v>
       </c>
       <c r="L22" s="10">
-        <v>-15.1</v>
+        <v>28.8</v>
       </c>
       <c r="M22" s="9">
-        <v>3.4</v>
-      </c>
-      <c r="N22" s="8">
-        <v>22.5</v>
-      </c>
-      <c r="O22" s="8">
-        <v>17.399999999999999</v>
+        <v>3.79</v>
+      </c>
+      <c r="N22" s="10">
+        <v>11.4</v>
+      </c>
+      <c r="O22" s="10">
+        <v>28.8</v>
       </c>
       <c r="P22" s="9">
-        <v>31.56</v>
+        <v>3.79</v>
       </c>
       <c r="Q22" s="10">
-        <v>-15.1</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B23" s="7">
-        <v>140</v>
+        <v>167.5</v>
       </c>
       <c r="C23" s="7">
-        <v>166.5</v>
+        <v>167</v>
       </c>
       <c r="D23" s="7">
-        <v>178</v>
+        <v>182.5</v>
       </c>
       <c r="E23" s="7">
-        <v>137</v>
-      </c>
-      <c r="F23" s="8">
-        <v>27.5</v>
-      </c>
-      <c r="G23" s="8">
-        <v>19.78</v>
+        <v>152</v>
+      </c>
+      <c r="F23" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="G23" s="10">
+        <v>0.3</v>
       </c>
       <c r="H23" s="9">
-        <v>2.77</v>
-      </c>
-      <c r="I23" s="8">
-        <v>6.22</v>
-      </c>
-      <c r="J23" s="8">
-        <v>2.44</v>
+        <v>3.4</v>
+      </c>
+      <c r="I23" s="10">
+        <v>22.5</v>
+      </c>
+      <c r="J23" s="10">
+        <v>17.399999999999999</v>
       </c>
       <c r="K23" s="9">
-        <v>28.16</v>
-      </c>
-      <c r="L23" s="10">
-        <v>-17.8</v>
+        <v>31.56</v>
+      </c>
+      <c r="L23" s="8">
+        <v>-15.1</v>
       </c>
       <c r="M23" s="9">
-        <v>2.77</v>
-      </c>
-      <c r="N23" s="8">
-        <v>6.22</v>
-      </c>
-      <c r="O23" s="8">
-        <v>2.44</v>
+        <v>3.4</v>
+      </c>
+      <c r="N23" s="10">
+        <v>22.5</v>
+      </c>
+      <c r="O23" s="10">
+        <v>17.399999999999999</v>
       </c>
       <c r="P23" s="9">
-        <v>28.16</v>
-      </c>
-      <c r="Q23" s="10">
-        <v>-17.8</v>
+        <v>31.56</v>
+      </c>
+      <c r="Q23" s="8">
+        <v>-15.1</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B24" s="7">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C24" s="7">
-        <v>139</v>
+        <v>166.5</v>
       </c>
       <c r="D24" s="7">
-        <v>156.5</v>
+        <v>178</v>
       </c>
       <c r="E24" s="7">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="F24" s="10">
-        <v>-8</v>
+        <v>27.5</v>
       </c>
       <c r="G24" s="10">
-        <v>-5.44</v>
+        <v>19.78</v>
       </c>
       <c r="H24" s="9">
-        <v>2.61</v>
-      </c>
-      <c r="I24" s="8">
-        <v>16.8</v>
-      </c>
-      <c r="J24" s="8">
-        <v>4.26</v>
+        <v>2.77</v>
+      </c>
+      <c r="I24" s="10">
+        <v>6.22</v>
+      </c>
+      <c r="J24" s="10">
+        <v>2.44</v>
       </c>
       <c r="K24" s="9">
-        <v>25.39</v>
-      </c>
-      <c r="L24" s="10">
-        <v>-19.600000000000001</v>
+        <v>28.16</v>
+      </c>
+      <c r="L24" s="8">
+        <v>-17.8</v>
       </c>
       <c r="M24" s="9">
-        <v>2.61</v>
-      </c>
-      <c r="N24" s="8">
-        <v>16.8</v>
-      </c>
-      <c r="O24" s="8">
-        <v>4.26</v>
+        <v>2.77</v>
+      </c>
+      <c r="N24" s="10">
+        <v>6.22</v>
+      </c>
+      <c r="O24" s="10">
+        <v>2.44</v>
       </c>
       <c r="P24" s="9">
-        <v>25.39</v>
-      </c>
-      <c r="Q24" s="10">
-        <v>-19.600000000000001</v>
+        <v>28.16</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>-17.8</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B25" s="7">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C25" s="7">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D25" s="7">
-        <v>173.5</v>
+        <v>156.5</v>
       </c>
       <c r="E25" s="7">
-        <v>139</v>
-      </c>
-      <c r="F25" s="10">
-        <v>-6</v>
-      </c>
-      <c r="G25" s="10">
-        <v>-3.92</v>
+        <v>131</v>
+      </c>
+      <c r="F25" s="8">
+        <v>-8</v>
+      </c>
+      <c r="G25" s="8">
+        <v>-5.44</v>
       </c>
       <c r="H25" s="9">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="I25" s="8">
-        <v>8.48</v>
+        <v>2.61</v>
+      </c>
+      <c r="I25" s="10">
+        <v>16.8</v>
       </c>
       <c r="J25" s="10">
-        <v>-9.74</v>
+        <v>4.26</v>
       </c>
       <c r="K25" s="9">
-        <v>22.78</v>
-      </c>
-      <c r="L25" s="10">
-        <v>-21.6</v>
+        <v>25.39</v>
+      </c>
+      <c r="L25" s="8">
+        <v>-19.600000000000001</v>
       </c>
       <c r="M25" s="9">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="N25" s="8">
-        <v>8.48</v>
+        <v>2.61</v>
+      </c>
+      <c r="N25" s="10">
+        <v>16.8</v>
       </c>
       <c r="O25" s="10">
-        <v>-9.74</v>
+        <v>4.26</v>
       </c>
       <c r="P25" s="9">
-        <v>22.78</v>
-      </c>
-      <c r="Q25" s="10">
-        <v>-21.6</v>
+        <v>25.39</v>
+      </c>
+      <c r="Q25" s="8">
+        <v>-19.600000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B26" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C26" s="7">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D26" s="7">
-        <v>164.5</v>
+        <v>173.5</v>
       </c>
       <c r="E26" s="7">
-        <v>130</v>
-      </c>
-      <c r="F26" s="10">
-        <v>-0.5</v>
-      </c>
-      <c r="G26" s="10">
-        <v>-0.33</v>
+        <v>139</v>
+      </c>
+      <c r="F26" s="8">
+        <v>-6</v>
+      </c>
+      <c r="G26" s="8">
+        <v>-3.92</v>
       </c>
       <c r="H26" s="9">
-        <v>2.06</v>
-      </c>
-      <c r="I26" s="8">
-        <v>1.18</v>
-      </c>
-      <c r="J26" s="10">
-        <v>-25.1</v>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="I26" s="10">
+        <v>8.48</v>
+      </c>
+      <c r="J26" s="8">
+        <v>-9.74</v>
       </c>
       <c r="K26" s="9">
-        <v>20.54</v>
-      </c>
-      <c r="L26" s="10">
-        <v>-22.7</v>
+        <v>22.78</v>
+      </c>
+      <c r="L26" s="8">
+        <v>-21.6</v>
       </c>
       <c r="M26" s="9">
-        <v>2.06</v>
-      </c>
-      <c r="N26" s="8">
-        <v>1.18</v>
-      </c>
-      <c r="O26" s="10">
-        <v>-25.1</v>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="N26" s="10">
+        <v>8.48</v>
+      </c>
+      <c r="O26" s="8">
+        <v>-9.74</v>
       </c>
       <c r="P26" s="9">
-        <v>20.54</v>
-      </c>
-      <c r="Q26" s="10">
-        <v>-22.7</v>
+        <v>22.78</v>
+      </c>
+      <c r="Q26" s="8">
+        <v>-21.6</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B27" s="7">
-        <v>165.5</v>
+        <v>155</v>
       </c>
       <c r="C27" s="7">
-        <v>153.5</v>
+        <v>153</v>
       </c>
       <c r="D27" s="7">
-        <v>193</v>
+        <v>164.5</v>
       </c>
       <c r="E27" s="7">
-        <v>138</v>
-      </c>
-      <c r="F27" s="10">
-        <v>-9.5</v>
-      </c>
-      <c r="G27" s="10">
-        <v>-5.83</v>
+        <v>130</v>
+      </c>
+      <c r="F27" s="8">
+        <v>-0.5</v>
+      </c>
+      <c r="G27" s="8">
+        <v>-0.33</v>
       </c>
       <c r="H27" s="9">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I27" s="10">
-        <v>-21.8</v>
-      </c>
-      <c r="J27" s="10">
-        <v>-41.5</v>
+        <v>1.18</v>
+      </c>
+      <c r="J27" s="8">
+        <v>-25.1</v>
       </c>
       <c r="K27" s="9">
-        <v>18.48</v>
-      </c>
-      <c r="L27" s="10">
-        <v>-22.5</v>
+        <v>20.54</v>
+      </c>
+      <c r="L27" s="8">
+        <v>-22.7</v>
       </c>
       <c r="M27" s="9">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="N27" s="10">
-        <v>-21.8</v>
-      </c>
-      <c r="O27" s="10">
-        <v>-41.5</v>
+        <v>1.18</v>
+      </c>
+      <c r="O27" s="8">
+        <v>-25.1</v>
       </c>
       <c r="P27" s="9">
-        <v>18.48</v>
-      </c>
-      <c r="Q27" s="10">
-        <v>-22.5</v>
+        <v>20.54</v>
+      </c>
+      <c r="Q27" s="8">
+        <v>-22.7</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B28" s="7">
-        <v>155.5</v>
+        <v>165.5</v>
       </c>
       <c r="C28" s="7">
-        <v>163</v>
+        <v>153.5</v>
       </c>
       <c r="D28" s="7">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="E28" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F28" s="8">
-        <v>9.5</v>
+        <v>-9.5</v>
       </c>
       <c r="G28" s="8">
-        <v>6.19</v>
+        <v>-5.83</v>
       </c>
       <c r="H28" s="9">
-        <v>2.6</v>
+        <v>2.04</v>
       </c>
       <c r="I28" s="8">
-        <v>2.86</v>
-      </c>
-      <c r="J28" s="10">
-        <v>-17.8</v>
+        <v>-21.8</v>
+      </c>
+      <c r="J28" s="8">
+        <v>-41.5</v>
       </c>
       <c r="K28" s="9">
-        <v>16.45</v>
-      </c>
-      <c r="L28" s="10">
-        <v>-19.2</v>
+        <v>18.48</v>
+      </c>
+      <c r="L28" s="8">
+        <v>-22.5</v>
       </c>
       <c r="M28" s="9">
-        <v>2.6</v>
+        <v>2.04</v>
       </c>
       <c r="N28" s="8">
-        <v>2.86</v>
-      </c>
-      <c r="O28" s="10">
-        <v>-17.8</v>
+        <v>-21.8</v>
+      </c>
+      <c r="O28" s="8">
+        <v>-41.5</v>
       </c>
       <c r="P28" s="9">
-        <v>16.45</v>
-      </c>
-      <c r="Q28" s="10">
-        <v>-19.2</v>
+        <v>18.48</v>
+      </c>
+      <c r="Q28" s="8">
+        <v>-22.5</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B29" s="7">
-        <v>88.2</v>
+        <v>155.5</v>
       </c>
       <c r="C29" s="7">
-        <v>153.5</v>
+        <v>163</v>
       </c>
       <c r="D29" s="7">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="E29" s="7">
-        <v>88.1</v>
-      </c>
-      <c r="F29" s="8">
-        <v>60.8</v>
-      </c>
-      <c r="G29" s="8">
-        <v>65.59</v>
+        <v>137</v>
+      </c>
+      <c r="F29" s="10">
+        <v>9.5</v>
+      </c>
+      <c r="G29" s="10">
+        <v>6.19</v>
       </c>
       <c r="H29" s="9">
-        <v>2.5299999999999998</v>
-      </c>
-      <c r="I29" s="8">
-        <v>5.51</v>
-      </c>
-      <c r="J29" s="10">
-        <v>-19.8</v>
+        <v>2.6</v>
+      </c>
+      <c r="I29" s="10">
+        <v>2.86</v>
+      </c>
+      <c r="J29" s="8">
+        <v>-17.8</v>
       </c>
       <c r="K29" s="9">
-        <v>13.84</v>
-      </c>
-      <c r="L29" s="10">
-        <v>-19.5</v>
+        <v>16.45</v>
+      </c>
+      <c r="L29" s="8">
+        <v>-19.2</v>
       </c>
       <c r="M29" s="9">
-        <v>2.5299999999999998</v>
-      </c>
-      <c r="N29" s="8">
-        <v>5.51</v>
-      </c>
-      <c r="O29" s="10">
-        <v>-19.8</v>
+        <v>2.6</v>
+      </c>
+      <c r="N29" s="10">
+        <v>2.86</v>
+      </c>
+      <c r="O29" s="8">
+        <v>-17.8</v>
       </c>
       <c r="P29" s="9">
-        <v>13.84</v>
-      </c>
-      <c r="Q29" s="10">
-        <v>-19.5</v>
+        <v>16.45</v>
+      </c>
+      <c r="Q29" s="8">
+        <v>-19.2</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B30" s="7">
-        <v>66.099999999999994</v>
+        <v>88.2</v>
       </c>
       <c r="C30" s="7">
-        <v>92.7</v>
+        <v>153.5</v>
       </c>
       <c r="D30" s="7">
-        <v>95.9</v>
+        <v>160</v>
       </c>
       <c r="E30" s="7">
-        <v>65.099999999999994</v>
-      </c>
-      <c r="F30" s="8">
-        <v>26.7</v>
-      </c>
-      <c r="G30" s="8">
-        <v>40.450000000000003</v>
+        <v>88.1</v>
+      </c>
+      <c r="F30" s="10">
+        <v>60.8</v>
+      </c>
+      <c r="G30" s="10">
+        <v>65.59</v>
       </c>
       <c r="H30" s="9">
-        <v>2.4</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="I30" s="10">
-        <v>-17.2</v>
-      </c>
-      <c r="J30" s="10">
-        <v>-46.6</v>
+        <v>5.51</v>
+      </c>
+      <c r="J30" s="8">
+        <v>-19.8</v>
       </c>
       <c r="K30" s="9">
-        <v>11.31</v>
-      </c>
-      <c r="L30" s="10">
-        <v>-19.399999999999999</v>
+        <v>13.84</v>
+      </c>
+      <c r="L30" s="8">
+        <v>-19.5</v>
       </c>
       <c r="M30" s="9">
-        <v>2.4</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="N30" s="10">
-        <v>-17.2</v>
-      </c>
-      <c r="O30" s="10">
-        <v>-46.6</v>
+        <v>5.51</v>
+      </c>
+      <c r="O30" s="8">
+        <v>-19.8</v>
       </c>
       <c r="P30" s="9">
-        <v>11.31</v>
-      </c>
-      <c r="Q30" s="10">
-        <v>-19.399999999999999</v>
+        <v>13.84</v>
+      </c>
+      <c r="Q30" s="8">
+        <v>-19.5</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B31" s="7">
-        <v>86.6</v>
+        <v>66.099999999999994</v>
       </c>
       <c r="C31" s="7">
-        <v>66</v>
+        <v>92.7</v>
       </c>
       <c r="D31" s="7">
-        <v>99.4</v>
+        <v>95.9</v>
       </c>
       <c r="E31" s="7">
-        <v>58.5</v>
+        <v>65.099999999999994</v>
       </c>
       <c r="F31" s="10">
-        <v>-28.6</v>
+        <v>26.7</v>
       </c>
       <c r="G31" s="10">
-        <v>-30.23</v>
+        <v>40.450000000000003</v>
       </c>
       <c r="H31" s="9">
-        <v>2.9</v>
-      </c>
-      <c r="I31" s="10">
-        <v>-5.79</v>
-      </c>
-      <c r="J31" s="10">
-        <v>-25.1</v>
+        <v>2.4</v>
+      </c>
+      <c r="I31" s="8">
+        <v>-17.2</v>
+      </c>
+      <c r="J31" s="8">
+        <v>-46.6</v>
       </c>
       <c r="K31" s="9">
-        <v>8.91</v>
-      </c>
-      <c r="L31" s="10">
-        <v>-6.55</v>
+        <v>11.31</v>
+      </c>
+      <c r="L31" s="8">
+        <v>-19.399999999999999</v>
       </c>
       <c r="M31" s="9">
-        <v>2.9</v>
-      </c>
-      <c r="N31" s="10">
-        <v>-5.79</v>
-      </c>
-      <c r="O31" s="10">
-        <v>-25.1</v>
+        <v>2.4</v>
+      </c>
+      <c r="N31" s="8">
+        <v>-17.2</v>
+      </c>
+      <c r="O31" s="8">
+        <v>-46.6</v>
       </c>
       <c r="P31" s="9">
-        <v>8.91</v>
-      </c>
-      <c r="Q31" s="10">
-        <v>-6.55</v>
+        <v>11.31</v>
+      </c>
+      <c r="Q31" s="8">
+        <v>-19.399999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="B32" s="7">
-        <v>105.5</v>
+        <v>86.6</v>
       </c>
       <c r="C32" s="7">
-        <v>94.6</v>
+        <v>66</v>
       </c>
       <c r="D32" s="7">
-        <v>117</v>
+        <v>99.4</v>
       </c>
       <c r="E32" s="7">
-        <v>94.4</v>
-      </c>
-      <c r="F32" s="10">
-        <v>-18.899999999999999</v>
-      </c>
-      <c r="G32" s="10">
-        <v>-16.649999999999999</v>
+        <v>58.5</v>
+      </c>
+      <c r="F32" s="8">
+        <v>-28.6</v>
+      </c>
+      <c r="G32" s="8">
+        <v>-30.23</v>
       </c>
       <c r="H32" s="9">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="I32" s="8">
-        <v>4.7</v>
+        <v>-5.79</v>
       </c>
       <c r="J32" s="8">
-        <v>37.200000000000003</v>
+        <v>-25.1</v>
       </c>
       <c r="K32" s="9">
-        <v>6.01</v>
+        <v>8.91</v>
       </c>
       <c r="L32" s="8">
-        <v>6.1</v>
+        <v>-6.55</v>
       </c>
       <c r="M32" s="9">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="N32" s="8">
-        <v>4.7</v>
+        <v>-5.79</v>
       </c>
       <c r="O32" s="8">
-        <v>37.200000000000003</v>
+        <v>-25.1</v>
       </c>
       <c r="P32" s="9">
-        <v>6.01</v>
+        <v>8.91</v>
       </c>
       <c r="Q32" s="8">
-        <v>6.1</v>
+        <v>-6.55</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B33" s="7">
-        <v>119</v>
+        <v>105.5</v>
       </c>
       <c r="C33" s="7">
-        <v>113.5</v>
+        <v>94.6</v>
       </c>
       <c r="D33" s="7">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="E33" s="7">
-        <v>105</v>
-      </c>
-      <c r="F33" s="10">
-        <v>-4.5</v>
-      </c>
-      <c r="G33" s="10">
-        <v>-3.81</v>
+        <v>94.4</v>
+      </c>
+      <c r="F33" s="8">
+        <v>-18.899999999999999</v>
+      </c>
+      <c r="G33" s="8">
+        <v>-16.649999999999999</v>
       </c>
       <c r="H33" s="9">
-        <v>2.94</v>
-      </c>
-      <c r="I33" s="8">
-        <v>1.58</v>
+        <v>3.08</v>
+      </c>
+      <c r="I33" s="10">
+        <v>4.7</v>
       </c>
       <c r="J33" s="10">
-        <v>-14.2</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="K33" s="9">
-        <v>2.94</v>
+        <v>6.01</v>
       </c>
       <c r="L33" s="10">
-        <v>-14.2</v>
+        <v>6.1</v>
       </c>
       <c r="M33" s="9">
-        <v>2.94</v>
-      </c>
-      <c r="N33" s="8">
-        <v>1.58</v>
+        <v>3.08</v>
+      </c>
+      <c r="N33" s="10">
+        <v>4.7</v>
       </c>
       <c r="O33" s="10">
-        <v>-14.2</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="P33" s="9">
-        <v>2.94</v>
+        <v>6.01</v>
       </c>
       <c r="Q33" s="10">
-        <v>-14.2</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43800</v>
+        <v>43831</v>
       </c>
       <c r="B34" s="7">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="C34" s="7">
-        <v>118</v>
+        <v>113.5</v>
       </c>
       <c r="D34" s="7">
-        <v>126.5</v>
+        <v>138</v>
       </c>
       <c r="E34" s="7">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="F34" s="8">
-        <v>62</v>
+        <v>-4.5</v>
       </c>
       <c r="G34" s="8">
-        <v>110.71</v>
+        <v>-3.81</v>
       </c>
       <c r="H34" s="9">
-        <v>2.89</v>
-      </c>
-      <c r="I34" s="8">
-        <v>6.82</v>
-      </c>
-      <c r="J34" s="10">
-        <v>-33.799999999999997</v>
+        <v>2.94</v>
+      </c>
+      <c r="I34" s="10">
+        <v>1.58</v>
+      </c>
+      <c r="J34" s="8">
+        <v>-14.2</v>
       </c>
       <c r="K34" s="9">
-        <v>37.17</v>
+        <v>2.94</v>
       </c>
       <c r="L34" s="8">
-        <v>18.100000000000001</v>
+        <v>-14.2</v>
       </c>
       <c r="M34" s="9">
-        <v>2.89</v>
-      </c>
-      <c r="N34" s="8">
-        <v>6.82</v>
-      </c>
-      <c r="O34" s="10">
-        <v>-33.799999999999997</v>
+        <v>2.94</v>
+      </c>
+      <c r="N34" s="10">
+        <v>1.58</v>
+      </c>
+      <c r="O34" s="8">
+        <v>-14.2</v>
       </c>
       <c r="P34" s="9">
-        <v>37.17</v>
+        <v>2.94</v>
       </c>
       <c r="Q34" s="8">
-        <v>18.100000000000001</v>
+        <v>-14.2</v>
       </c>
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43770</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>17</v>
+        <v>43800</v>
+      </c>
+      <c r="B35" s="7">
+        <v>80</v>
+      </c>
+      <c r="C35" s="7">
+        <v>118</v>
+      </c>
+      <c r="D35" s="7">
+        <v>126.5</v>
+      </c>
+      <c r="E35" s="7">
+        <v>79</v>
+      </c>
+      <c r="F35" s="10">
+        <v>62</v>
+      </c>
+      <c r="G35" s="10">
+        <v>110.71</v>
       </c>
       <c r="H35" s="9">
-        <v>2.71</v>
-      </c>
-      <c r="I35" s="8">
-        <v>8.11</v>
-      </c>
-      <c r="J35" s="10">
-        <v>-33.299999999999997</v>
+        <v>2.89</v>
+      </c>
+      <c r="I35" s="10">
+        <v>6.82</v>
+      </c>
+      <c r="J35" s="8">
+        <v>-33.799999999999997</v>
       </c>
       <c r="K35" s="9">
-        <v>34.28</v>
-      </c>
-      <c r="L35" s="8">
-        <v>26.5</v>
+        <v>37.17</v>
+      </c>
+      <c r="L35" s="10">
+        <v>18.100000000000001</v>
       </c>
       <c r="M35" s="9">
-        <v>2.71</v>
-      </c>
-      <c r="N35" s="8">
-        <v>8.11</v>
-      </c>
-      <c r="O35" s="10">
-        <v>-33.299999999999997</v>
+        <v>2.89</v>
+      </c>
+      <c r="N35" s="10">
+        <v>6.82</v>
+      </c>
+      <c r="O35" s="8">
+        <v>-33.799999999999997</v>
       </c>
       <c r="P35" s="9">
-        <v>34.28</v>
-      </c>
-      <c r="Q35" s="8">
-        <v>26.5</v>
+        <v>37.17</v>
+      </c>
+      <c r="Q35" s="10">
+        <v>18.100000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>17</v>
@@ -3046,39 +3046,39 @@
         <v>17</v>
       </c>
       <c r="H36" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="I36" s="8">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="J36" s="10">
-        <v>-34.4</v>
+        <v>2.71</v>
+      </c>
+      <c r="I36" s="10">
+        <v>8.11</v>
+      </c>
+      <c r="J36" s="8">
+        <v>-33.299999999999997</v>
       </c>
       <c r="K36" s="9">
-        <v>31.57</v>
-      </c>
-      <c r="L36" s="8">
-        <v>37</v>
+        <v>34.28</v>
+      </c>
+      <c r="L36" s="10">
+        <v>26.5</v>
       </c>
       <c r="M36" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="N36" s="8">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="O36" s="10">
-        <v>-34.4</v>
+        <v>2.71</v>
+      </c>
+      <c r="N36" s="10">
+        <v>8.11</v>
+      </c>
+      <c r="O36" s="8">
+        <v>-33.299999999999997</v>
       </c>
       <c r="P36" s="9">
-        <v>31.57</v>
-      </c>
-      <c r="Q36" s="8">
-        <v>37</v>
+        <v>34.28</v>
+      </c>
+      <c r="Q36" s="10">
+        <v>26.5</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>43709</v>
+        <v>43739</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>17</v>
@@ -3099,39 +3099,39 @@
         <v>17</v>
       </c>
       <c r="H37" s="9">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I37" s="10">
-        <v>-9.94</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="J37" s="8">
-        <v>327.3</v>
+        <v>-34.4</v>
       </c>
       <c r="K37" s="9">
-        <v>29.07</v>
-      </c>
-      <c r="L37" s="8">
-        <v>51.2</v>
+        <v>31.57</v>
+      </c>
+      <c r="L37" s="10">
+        <v>37</v>
       </c>
       <c r="M37" s="9">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="N37" s="10">
-        <v>-9.94</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="O37" s="8">
-        <v>327.3</v>
+        <v>-34.4</v>
       </c>
       <c r="P37" s="9">
-        <v>29.07</v>
-      </c>
-      <c r="Q37" s="8">
-        <v>51.2</v>
+        <v>31.57</v>
+      </c>
+      <c r="Q37" s="10">
+        <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>43678</v>
+        <v>43709</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>17</v>
@@ -3152,39 +3152,39 @@
         <v>17</v>
       </c>
       <c r="H38" s="9">
-        <v>2.75</v>
-      </c>
-      <c r="I38" s="10">
-        <v>-21</v>
-      </c>
-      <c r="J38" s="8">
-        <v>27.5</v>
+        <v>2.48</v>
+      </c>
+      <c r="I38" s="8">
+        <v>-9.94</v>
+      </c>
+      <c r="J38" s="10">
+        <v>327.3</v>
       </c>
       <c r="K38" s="9">
-        <v>26.59</v>
-      </c>
-      <c r="L38" s="8">
-        <v>42.6</v>
+        <v>29.07</v>
+      </c>
+      <c r="L38" s="10">
+        <v>51.2</v>
       </c>
       <c r="M38" s="9">
-        <v>2.75</v>
-      </c>
-      <c r="N38" s="10">
-        <v>-21</v>
-      </c>
-      <c r="O38" s="8">
-        <v>27.5</v>
+        <v>2.48</v>
+      </c>
+      <c r="N38" s="8">
+        <v>-9.94</v>
+      </c>
+      <c r="O38" s="10">
+        <v>327.3</v>
       </c>
       <c r="P38" s="9">
-        <v>26.59</v>
-      </c>
-      <c r="Q38" s="8">
-        <v>42.6</v>
+        <v>29.07</v>
+      </c>
+      <c r="Q38" s="10">
+        <v>51.2</v>
       </c>
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>43647</v>
+        <v>43678</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>17</v>
@@ -3205,39 +3205,39 @@
         <v>17</v>
       </c>
       <c r="H39" s="9">
-        <v>3.48</v>
+        <v>2.75</v>
       </c>
       <c r="I39" s="8">
-        <v>10</v>
-      </c>
-      <c r="J39" s="8">
-        <v>299</v>
+        <v>-21</v>
+      </c>
+      <c r="J39" s="10">
+        <v>27.5</v>
       </c>
       <c r="K39" s="9">
-        <v>23.84</v>
-      </c>
-      <c r="L39" s="8">
-        <v>44.6</v>
+        <v>26.59</v>
+      </c>
+      <c r="L39" s="10">
+        <v>42.6</v>
       </c>
       <c r="M39" s="9">
-        <v>3.48</v>
+        <v>2.75</v>
       </c>
       <c r="N39" s="8">
-        <v>10</v>
-      </c>
-      <c r="O39" s="8">
-        <v>299</v>
+        <v>-21</v>
+      </c>
+      <c r="O39" s="10">
+        <v>27.5</v>
       </c>
       <c r="P39" s="9">
-        <v>23.84</v>
-      </c>
-      <c r="Q39" s="8">
-        <v>44.6</v>
+        <v>26.59</v>
+      </c>
+      <c r="Q39" s="10">
+        <v>42.6</v>
       </c>
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>43617</v>
+        <v>43647</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>17</v>
@@ -3258,39 +3258,39 @@
         <v>17</v>
       </c>
       <c r="H40" s="9">
-        <v>3.17</v>
-      </c>
-      <c r="I40" s="8">
-        <v>0.24</v>
-      </c>
-      <c r="J40" s="8">
-        <v>212.7</v>
+        <v>3.48</v>
+      </c>
+      <c r="I40" s="10">
+        <v>10</v>
+      </c>
+      <c r="J40" s="10">
+        <v>299</v>
       </c>
       <c r="K40" s="9">
-        <v>20.36</v>
-      </c>
-      <c r="L40" s="8">
-        <v>30.4</v>
+        <v>23.84</v>
+      </c>
+      <c r="L40" s="10">
+        <v>44.6</v>
       </c>
       <c r="M40" s="9">
-        <v>3.17</v>
-      </c>
-      <c r="N40" s="8">
-        <v>0.24</v>
-      </c>
-      <c r="O40" s="8">
-        <v>212.7</v>
+        <v>3.48</v>
+      </c>
+      <c r="N40" s="10">
+        <v>10</v>
+      </c>
+      <c r="O40" s="10">
+        <v>299</v>
       </c>
       <c r="P40" s="9">
-        <v>20.36</v>
-      </c>
-      <c r="Q40" s="8">
-        <v>30.4</v>
+        <v>23.84</v>
+      </c>
+      <c r="Q40" s="10">
+        <v>44.6</v>
       </c>
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>43586</v>
+        <v>43617</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>17</v>
@@ -3311,39 +3311,39 @@
         <v>17</v>
       </c>
       <c r="H41" s="9">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="I41" s="10">
-        <v>-29.8</v>
-      </c>
-      <c r="J41" s="8">
-        <v>3.82</v>
+        <v>0.24</v>
+      </c>
+      <c r="J41" s="10">
+        <v>212.7</v>
       </c>
       <c r="K41" s="9">
-        <v>17.190000000000001</v>
-      </c>
-      <c r="L41" s="8">
-        <v>17.8</v>
+        <v>20.36</v>
+      </c>
+      <c r="L41" s="10">
+        <v>30.4</v>
       </c>
       <c r="M41" s="9">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="N41" s="10">
-        <v>-29.8</v>
-      </c>
-      <c r="O41" s="8">
-        <v>3.82</v>
+        <v>0.24</v>
+      </c>
+      <c r="O41" s="10">
+        <v>212.7</v>
       </c>
       <c r="P41" s="9">
-        <v>17.190000000000001</v>
-      </c>
-      <c r="Q41" s="8">
-        <v>17.8</v>
+        <v>20.36</v>
+      </c>
+      <c r="Q41" s="10">
+        <v>30.4</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>43556</v>
+        <v>43586</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>17</v>
@@ -3364,39 +3364,39 @@
         <v>17</v>
       </c>
       <c r="H42" s="9">
-        <v>4.5</v>
+        <v>3.16</v>
       </c>
       <c r="I42" s="8">
-        <v>16.2</v>
-      </c>
-      <c r="J42" s="8">
-        <v>90.5</v>
+        <v>-29.8</v>
+      </c>
+      <c r="J42" s="10">
+        <v>3.82</v>
       </c>
       <c r="K42" s="9">
-        <v>14.03</v>
-      </c>
-      <c r="L42" s="8">
-        <v>21.4</v>
+        <v>17.190000000000001</v>
+      </c>
+      <c r="L42" s="10">
+        <v>17.8</v>
       </c>
       <c r="M42" s="9">
-        <v>4.5</v>
+        <v>3.16</v>
       </c>
       <c r="N42" s="8">
-        <v>16.2</v>
-      </c>
-      <c r="O42" s="8">
-        <v>90.5</v>
+        <v>-29.8</v>
+      </c>
+      <c r="O42" s="10">
+        <v>3.82</v>
       </c>
       <c r="P42" s="9">
-        <v>14.03</v>
-      </c>
-      <c r="Q42" s="8">
-        <v>21.4</v>
+        <v>17.190000000000001</v>
+      </c>
+      <c r="Q42" s="10">
+        <v>17.8</v>
       </c>
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>43525</v>
+        <v>43556</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>17</v>
@@ -3417,39 +3417,39 @@
         <v>17</v>
       </c>
       <c r="H43" s="9">
-        <v>3.87</v>
-      </c>
-      <c r="I43" s="8">
-        <v>72.599999999999994</v>
-      </c>
-      <c r="J43" s="8">
-        <v>18.3</v>
+        <v>4.5</v>
+      </c>
+      <c r="I43" s="10">
+        <v>16.2</v>
+      </c>
+      <c r="J43" s="10">
+        <v>90.5</v>
       </c>
       <c r="K43" s="9">
-        <v>9.5399999999999991</v>
-      </c>
-      <c r="L43" s="8">
-        <v>3.68</v>
+        <v>14.03</v>
+      </c>
+      <c r="L43" s="10">
+        <v>21.4</v>
       </c>
       <c r="M43" s="9">
-        <v>3.87</v>
-      </c>
-      <c r="N43" s="8">
-        <v>72.599999999999994</v>
-      </c>
-      <c r="O43" s="8">
-        <v>18.3</v>
+        <v>4.5</v>
+      </c>
+      <c r="N43" s="10">
+        <v>16.2</v>
+      </c>
+      <c r="O43" s="10">
+        <v>90.5</v>
       </c>
       <c r="P43" s="9">
-        <v>9.5399999999999991</v>
-      </c>
-      <c r="Q43" s="8">
-        <v>3.68</v>
+        <v>14.03</v>
+      </c>
+      <c r="Q43" s="10">
+        <v>21.4</v>
       </c>
     </row>
     <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>43497</v>
+        <v>43525</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>17</v>
@@ -3470,39 +3470,39 @@
         <v>17</v>
       </c>
       <c r="H44" s="9">
-        <v>2.2400000000000002</v>
+        <v>3.87</v>
       </c>
       <c r="I44" s="10">
-        <v>-34.6</v>
+        <v>72.599999999999994</v>
       </c>
       <c r="J44" s="10">
-        <v>-25.7</v>
+        <v>18.3</v>
       </c>
       <c r="K44" s="9">
-        <v>5.67</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="L44" s="10">
-        <v>-4.38</v>
+        <v>3.68</v>
       </c>
       <c r="M44" s="9">
-        <v>2.2400000000000002</v>
+        <v>3.87</v>
       </c>
       <c r="N44" s="10">
-        <v>-34.6</v>
+        <v>72.599999999999994</v>
       </c>
       <c r="O44" s="10">
-        <v>-25.7</v>
+        <v>18.3</v>
       </c>
       <c r="P44" s="9">
-        <v>5.67</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="Q44" s="10">
-        <v>-4.38</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>43466</v>
+        <v>43497</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>17</v>
@@ -3523,39 +3523,39 @@
         <v>17</v>
       </c>
       <c r="H45" s="9">
-        <v>3.43</v>
-      </c>
-      <c r="I45" s="10">
-        <v>-21.6</v>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="I45" s="8">
+        <v>-34.6</v>
       </c>
       <c r="J45" s="8">
-        <v>17.7</v>
+        <v>-25.7</v>
       </c>
       <c r="K45" s="9">
-        <v>3.43</v>
+        <v>5.67</v>
       </c>
       <c r="L45" s="8">
-        <v>17.7</v>
+        <v>-4.38</v>
       </c>
       <c r="M45" s="9">
-        <v>3.43</v>
-      </c>
-      <c r="N45" s="10">
-        <v>-21.6</v>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="N45" s="8">
+        <v>-34.6</v>
       </c>
       <c r="O45" s="8">
-        <v>17.7</v>
+        <v>-25.7</v>
       </c>
       <c r="P45" s="9">
-        <v>3.43</v>
+        <v>5.67</v>
       </c>
       <c r="Q45" s="8">
-        <v>17.7</v>
+        <v>-4.38</v>
       </c>
     </row>
     <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>43435</v>
+        <v>43466</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>17</v>
@@ -3576,39 +3576,39 @@
         <v>17</v>
       </c>
       <c r="H46" s="9">
-        <v>4.37</v>
+        <v>3.43</v>
       </c>
       <c r="I46" s="8">
-        <v>7.72</v>
-      </c>
-      <c r="J46" s="8">
-        <v>189.4</v>
+        <v>-21.6</v>
+      </c>
+      <c r="J46" s="10">
+        <v>17.7</v>
       </c>
       <c r="K46" s="9">
-        <v>31.48</v>
+        <v>3.43</v>
       </c>
       <c r="L46" s="10">
-        <v>-7.11</v>
+        <v>17.7</v>
       </c>
       <c r="M46" s="9">
-        <v>4.37</v>
+        <v>3.43</v>
       </c>
       <c r="N46" s="8">
-        <v>7.72</v>
-      </c>
-      <c r="O46" s="8">
-        <v>189.4</v>
+        <v>-21.6</v>
+      </c>
+      <c r="O46" s="10">
+        <v>17.7</v>
       </c>
       <c r="P46" s="9">
-        <v>31.48</v>
+        <v>3.43</v>
       </c>
       <c r="Q46" s="10">
-        <v>-7.11</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>43405</v>
+        <v>43435</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>17</v>
@@ -3629,39 +3629,39 @@
         <v>17</v>
       </c>
       <c r="H47" s="9">
-        <v>4.0599999999999996</v>
-      </c>
-      <c r="I47" s="8">
-        <v>6.28</v>
-      </c>
-      <c r="J47" s="8">
-        <v>5.59</v>
+        <v>4.37</v>
+      </c>
+      <c r="I47" s="10">
+        <v>7.72</v>
+      </c>
+      <c r="J47" s="10">
+        <v>189.4</v>
       </c>
       <c r="K47" s="9">
-        <v>27.1</v>
-      </c>
-      <c r="L47" s="10">
-        <v>-16.3</v>
+        <v>31.48</v>
+      </c>
+      <c r="L47" s="8">
+        <v>-7.11</v>
       </c>
       <c r="M47" s="9">
-        <v>4.0599999999999996</v>
-      </c>
-      <c r="N47" s="8">
-        <v>6.28</v>
-      </c>
-      <c r="O47" s="8">
-        <v>5.59</v>
+        <v>4.37</v>
+      </c>
+      <c r="N47" s="10">
+        <v>7.72</v>
+      </c>
+      <c r="O47" s="10">
+        <v>189.4</v>
       </c>
       <c r="P47" s="9">
-        <v>27.1</v>
-      </c>
-      <c r="Q47" s="10">
-        <v>-16.3</v>
+        <v>31.48</v>
+      </c>
+      <c r="Q47" s="8">
+        <v>-7.11</v>
       </c>
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>43374</v>
+        <v>43405</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>17</v>
@@ -3682,39 +3682,39 @@
         <v>17</v>
       </c>
       <c r="H48" s="9">
-        <v>3.82</v>
-      </c>
-      <c r="I48" s="8">
-        <v>558.70000000000005</v>
-      </c>
-      <c r="J48" s="8">
-        <v>53.5</v>
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="I48" s="10">
+        <v>6.28</v>
+      </c>
+      <c r="J48" s="10">
+        <v>5.59</v>
       </c>
       <c r="K48" s="9">
-        <v>23.04</v>
-      </c>
-      <c r="L48" s="10">
-        <v>-19.2</v>
+        <v>27.1</v>
+      </c>
+      <c r="L48" s="8">
+        <v>-16.3</v>
       </c>
       <c r="M48" s="9">
-        <v>3.82</v>
-      </c>
-      <c r="N48" s="8">
-        <v>558.70000000000005</v>
-      </c>
-      <c r="O48" s="8">
-        <v>53.5</v>
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="N48" s="10">
+        <v>6.28</v>
+      </c>
+      <c r="O48" s="10">
+        <v>5.59</v>
       </c>
       <c r="P48" s="9">
-        <v>23.04</v>
-      </c>
-      <c r="Q48" s="10">
-        <v>-19.2</v>
+        <v>27.1</v>
+      </c>
+      <c r="Q48" s="8">
+        <v>-16.3</v>
       </c>
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>43344</v>
+        <v>43374</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>17</v>
@@ -3735,86 +3735,139 @@
         <v>17</v>
       </c>
       <c r="H49" s="9">
-        <v>0.57999999999999996</v>
+        <v>3.82</v>
       </c>
       <c r="I49" s="10">
-        <v>-73.099999999999994</v>
+        <v>558.70000000000005</v>
       </c>
       <c r="J49" s="10">
-        <v>-82.5</v>
+        <v>53.5</v>
       </c>
       <c r="K49" s="9">
-        <v>19.23</v>
-      </c>
-      <c r="L49" s="10">
-        <v>-26.2</v>
+        <v>23.04</v>
+      </c>
+      <c r="L49" s="8">
+        <v>-19.2</v>
       </c>
       <c r="M49" s="9">
-        <v>0.57999999999999996</v>
+        <v>3.82</v>
       </c>
       <c r="N49" s="10">
-        <v>-73.099999999999994</v>
+        <v>558.70000000000005</v>
       </c>
       <c r="O49" s="10">
-        <v>-82.5</v>
+        <v>53.5</v>
       </c>
       <c r="P49" s="9">
-        <v>19.23</v>
-      </c>
-      <c r="Q49" s="10">
-        <v>-26.2</v>
+        <v>23.04</v>
+      </c>
+      <c r="Q49" s="8">
+        <v>-19.2</v>
       </c>
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
+        <v>43344</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H50" s="9">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="I50" s="8">
+        <v>-73.099999999999994</v>
+      </c>
+      <c r="J50" s="8">
+        <v>-82.5</v>
+      </c>
+      <c r="K50" s="9">
+        <v>19.23</v>
+      </c>
+      <c r="L50" s="8">
+        <v>-26.2</v>
+      </c>
+      <c r="M50" s="9">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="N50" s="8">
+        <v>-73.099999999999994</v>
+      </c>
+      <c r="O50" s="8">
+        <v>-82.5</v>
+      </c>
+      <c r="P50" s="9">
+        <v>19.23</v>
+      </c>
+      <c r="Q50" s="8">
+        <v>-26.2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
         <v>43313</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H50" s="9">
+      <c r="B51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H51" s="9">
         <v>2.16</v>
       </c>
-      <c r="I50" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J50" s="10">
+      <c r="I51" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" s="8">
         <v>-44.3</v>
       </c>
-      <c r="K50" s="9">
+      <c r="K51" s="9">
         <v>18.649999999999999</v>
       </c>
-      <c r="L50" s="10">
+      <c r="L51" s="8">
         <v>-17.899999999999999</v>
       </c>
-      <c r="M50" s="9">
+      <c r="M51" s="9">
         <v>2.16</v>
       </c>
-      <c r="N50" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O50" s="10">
+      <c r="N51" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O51" s="8">
         <v>-44.3</v>
       </c>
-      <c r="P50" s="9">
+      <c r="P51" s="9">
         <v>18.649999999999999</v>
       </c>
-      <c r="Q50" s="10">
+      <c r="Q51" s="8">
         <v>-17.899999999999999</v>
       </c>
     </row>
